--- a/nriss-patch-2/ig/StructureDefinition-fr-observation-pregnancy-history-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-observation-pregnancy-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:58:47+00:00</t>
+    <t>2026-08-04T07:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-2/ig/StructureDefinition-fr-observation-pregnancy-history-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-observation-pregnancy-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:44:41+00:00</t>
+    <t>2026-08-07T09:15:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1500,7 +1500,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-pregnancy-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-birth-event-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-pregnancy-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1948,7 +1948,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="190.62890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
